--- a/src/moodys_datahub/data/products.xlsx
+++ b/src/moodys_datahub/data/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_lib_cbs_dk/Documents/Desktop/241031_Elisa_Sabbadin/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_libas_cbs_dk/Documents/Desktop/moody-s_datahub/src/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="50" documentId="8_{878F10CF-7955-491B-8F8B-956D1E605C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36065365-E65F-48DE-84A4-6AFEAD8F8A99}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{95D8BC7B-D8C9-4298-9EA2-4D3ACA8B17DE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{95D8BC7B-D8C9-4298-9EA2-4D3ACA8B17DE}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
